--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repos\mn_data_redesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3339A67D-734B-447C-9392-BBBA5305830B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E27B57-9244-404F-BA1B-D96551EABAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="20832" windowHeight="16656" xr2:uid="{8FBAF839-E732-4364-B5DC-26B38382FF1D}"/>
   </bookViews>
@@ -20,13 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
-  <si>
-    <t>搞定?</t>
-  </si>
-  <si>
-    <t>表名</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>说明</t>
   </si>
@@ -134,11 +128,23 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>dws_user_flagged_i_d</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>ads_cn.ads_user_flagged_i_d</t>
+  </si>
+  <si>
+    <t>落表</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>.sql 文件名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ads_user_flagged_i_d</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1136,180 +1142,222 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D639A680-3387-4533-8FC5-EB02377F5246}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.88671875" customWidth="1"/>
+    <col min="1" max="1" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="B14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="1" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
